--- a/sampleprojects/TaxReturn/excel/states/MI.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/MI.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>DT: MI Tax</t>
   </si>
@@ -147,7 +147,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(16 attributes)</t>
+    <t>(15 attributes)</t>
   </si>
   <si>
     <t>mi_adjusted_agi</t>
@@ -268,12 +268,6 @@
   </si>
   <si>
     <t>Total MI military income exclusion (computed). Sum of military retirement and SBP exclusions</t>
-  </si>
-  <si>
-    <t>state_tax_liability</t>
-  </si>
-  <si>
-    <t>MI state income tax liability</t>
   </si>
 </sst>
 </file>
@@ -2300,47 +2294,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>